--- a/education_forms/044_data_literacy_for_teachers_registration_form--education_forms.xlsx
+++ b/education_forms/044_data_literacy_for_teachers_registration_form--education_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
     <col width="25" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
     <col width="33" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -790,7 +790,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>course length unit</t>
+          <t>Course Length Unit Hint</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -894,7 +894,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>participant status</t>
+          <t>Participant Status Hint</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -944,7 +944,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>course status</t>
+          <t>Course Status Hint</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>program status</t>
+          <t>Program Status Hint</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1044,7 +1044,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>participant notes</t>
+          <t>Participant Notes Hint</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>course notes</t>
+          <t>Course Notes Hint</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
